--- a/6.2 Geoffrey Bay/output/Rugosity_growth_param_0.5.xlsx
+++ b/6.2 Geoffrey Bay/output/Rugosity_growth_param_0.5.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9901299015928973</v>
+        <v>1.005296640607698</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.00240655339484</v>
+        <v>1.032627004970806</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.019903617845217</v>
+        <v>1.064019408626427</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.044902842367905</v>
+        <v>1.103200129652486</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.074146146017215</v>
+        <v>1.145535762266584</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9126042849624818</v>
+        <v>0.9599754410171434</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.830184208505598</v>
+        <v>0.8649424674748475</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.876101748328916</v>
+        <v>0.920430187751571</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9271649557739247</v>
+        <v>0.980882325497177</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.981810590044161</v>
+        <v>1.045618924048626</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.041643432135824</v>
+        <v>1.116155539390397</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9063393581991057</v>
+        <v>0.9612734476163087</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.935893050220843</v>
+        <v>0.9919862773714778</v>
       </c>
     </row>
     <row r="16">
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9963785719307572</v>
+        <v>1.059507379630269</v>
       </c>
     </row>
     <row r="17">
@@ -560,7 +560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9646315573629621</v>
+        <v>1.023715014251389</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.024218813793786</v>
+        <v>1.089570520661568</v>
       </c>
     </row>
     <row r="19">
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.052994208633271</v>
+        <v>1.121099532261149</v>
       </c>
     </row>
     <row r="20">
@@ -584,7 +584,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.115500577979939</v>
+        <v>1.192200070450787</v>
       </c>
     </row>
     <row r="21">
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9777572635147266</v>
+        <v>1.042222336359344</v>
       </c>
     </row>
   </sheetData>
